--- a/artfynd/A 8133-2026 artfynd.xlsx
+++ b/artfynd/A 8133-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>88891675</v>
+        <v>55250380</v>
       </c>
       <c r="B2" t="n">
-        <v>90008</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108311</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,48 +686,52 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6031</v>
+        <v>648</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Klotullört</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Filago vulgaris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>Lam.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tåstarps backaväg 3, Sk</t>
+          <t>Tåstarps backaväg Dalagård, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>374447.5694768263</v>
+        <v>374376</v>
       </c>
       <c r="R2" t="n">
-        <v>6240351.493969426</v>
+        <v>6240291</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,22 +755,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-10-29</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-08-22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-10-29</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-08-22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,13 +769,12 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>granskog, moränkulle</t>
+          <t>grusbelagd vändplats för skogsavverkning</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -801,6 +789,120 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>88891675</v>
+      </c>
+      <c r="B3" t="n">
+        <v>92567</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Tåstarps backaväg 3, Sk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>374448</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6240351</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ängelholm</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Tåstarp</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2020-10-29</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2020-10-29</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>granskog, moränkulle</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Joachim Falck</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Joachim Falck</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
